--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021369</v>
+        <v>130020605</v>
       </c>
       <c r="B16" t="n">
-        <v>91625</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,30 +2329,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452811</v>
+        <v>452930</v>
       </c>
       <c r="R16" t="n">
-        <v>7044305</v>
+        <v>7044128</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,69 +2394,107 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt och med långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130021384</v>
+        <v>130020592</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>92058</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452906</v>
+        <v>452937</v>
       </c>
       <c r="R17" t="n">
-        <v>7044060</v>
+        <v>7044107</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2531,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,28 +2540,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130020605</v>
+        <v>130020591</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,26 +2595,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2551,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452930</v>
+        <v>452849</v>
       </c>
       <c r="R18" t="n">
-        <v>7044128</v>
+        <v>7044229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2666,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,22 +2686,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2644,41 +2719,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130020592</v>
+        <v>130020594</v>
       </c>
       <c r="B19" t="n">
-        <v>92058</v>
+        <v>97668</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2686,10 +2758,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452937</v>
+        <v>452919</v>
       </c>
       <c r="R19" t="n">
-        <v>7044107</v>
+        <v>7044111</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,11 +2796,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växer i en grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2742,26 +2809,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2779,10 +2826,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130020591</v>
+        <v>130021369</v>
       </c>
       <c r="B20" t="n">
-        <v>80193</v>
+        <v>91625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,41 +2837,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452849</v>
+        <v>452811</v>
       </c>
       <c r="R20" t="n">
-        <v>7044229</v>
+        <v>7044305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,104 +2895,69 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130020594</v>
+        <v>130021384</v>
       </c>
       <c r="B21" t="n">
-        <v>97668</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452919</v>
+        <v>452906</v>
       </c>
       <c r="R21" t="n">
-        <v>7044111</v>
+        <v>7044060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,82 +2992,74 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130020589</v>
+        <v>130021383</v>
       </c>
       <c r="B22" t="n">
-        <v>80221</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452853</v>
+        <v>453051</v>
       </c>
       <c r="R22" t="n">
-        <v>7044232</v>
+        <v>7044264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3103,7 +3096,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3112,81 +3105,59 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130020600</v>
+        <v>130020589</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3194,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452761</v>
+        <v>452853</v>
       </c>
       <c r="R23" t="n">
-        <v>7044258</v>
+        <v>7044232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3232,6 +3203,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3249,22 +3225,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3282,7 +3258,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021383</v>
+        <v>130020600</v>
       </c>
       <c r="B24" t="n">
         <v>79087</v>
@@ -3311,16 +3287,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453051</v>
+        <v>452761</v>
       </c>
       <c r="R24" t="n">
-        <v>7044264</v>
+        <v>7044258</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3355,29 +3334,50 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021368</v>
+        <v>130021371</v>
       </c>
       <c r="B2" t="n">
-        <v>91619</v>
+        <v>91626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452923</v>
+        <v>453025</v>
       </c>
       <c r="R2" t="n">
-        <v>7044088</v>
+        <v>7044138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021371</v>
+        <v>130021368</v>
       </c>
       <c r="B3" t="n">
-        <v>91625</v>
+        <v>91620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453025</v>
+        <v>452923</v>
       </c>
       <c r="R3" t="n">
-        <v>7044138</v>
+        <v>7044088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
         <v>130021381</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>130020602</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>130020606</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>130021386</v>
       </c>
       <c r="B7" t="n">
-        <v>89004</v>
+        <v>89005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130020604</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021365</v>
+        <v>130020599</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452913</v>
+        <v>452976</v>
       </c>
       <c r="R9" t="n">
-        <v>7044076</v>
+        <v>7044174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1530,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,18 +1539,44 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1656,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130020599</v>
+        <v>130021365</v>
       </c>
       <c r="B11" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,37 +1696,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452976</v>
+        <v>452913</v>
       </c>
       <c r="R11" t="n">
-        <v>7044174</v>
+        <v>7044076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1760,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,44 +1769,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
         <v>130020598</v>
       </c>
       <c r="B12" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>130020588</v>
       </c>
       <c r="B13" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>130020601</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>130020597</v>
       </c>
       <c r="B15" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2318,37 +2318,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130020605</v>
+        <v>130020592</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>92059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2356,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452930</v>
+        <v>452937</v>
       </c>
       <c r="R16" t="n">
-        <v>7044128</v>
+        <v>7044107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2400,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,12 +2430,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2449,52 +2453,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130020592</v>
+        <v>130021384</v>
       </c>
       <c r="B17" t="n">
-        <v>92058</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452937</v>
+        <v>452906</v>
       </c>
       <c r="R17" t="n">
-        <v>7044107</v>
+        <v>7044060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,7 +2528,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer i en grov granlåga.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,54 +2537,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130020591</v>
+        <v>130020605</v>
       </c>
       <c r="B18" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,30 +2566,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2626,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452849</v>
+        <v>452930</v>
       </c>
       <c r="R18" t="n">
-        <v>7044229</v>
+        <v>7044128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2633,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt och med långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,22 +2653,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2722,7 +2689,7 @@
         <v>130020594</v>
       </c>
       <c r="B19" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021369</v>
+        <v>130020591</v>
       </c>
       <c r="B20" t="n">
-        <v>91625</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,30 +2804,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452811</v>
+        <v>452849</v>
       </c>
       <c r="R20" t="n">
-        <v>7044305</v>
+        <v>7044229</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2895,34 +2873,65 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021384</v>
+        <v>130021369</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,23 +2939,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2954,10 +2959,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452906</v>
+        <v>452811</v>
       </c>
       <c r="R21" t="n">
-        <v>7044060</v>
+        <v>7044305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,11 +2995,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130021383</v>
+        <v>130020600</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453051</v>
+        <v>452761</v>
       </c>
       <c r="R22" t="n">
-        <v>7044264</v>
+        <v>7044258</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,81 +3097,95 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130020589</v>
+        <v>130021383</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452853</v>
+        <v>453051</v>
       </c>
       <c r="R23" t="n">
-        <v>7044232</v>
+        <v>7044264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,7 +3222,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,81 +3231,59 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130020600</v>
+        <v>130020589</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>80222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3296,10 +3291,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452761</v>
+        <v>452853</v>
       </c>
       <c r="R24" t="n">
-        <v>7044258</v>
+        <v>7044232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3334,6 +3329,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3500,7 +3500,7 @@
         <v>130020607</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>130021382</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>130021379</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>130021370</v>
       </c>
       <c r="B29" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>130020593</v>
       </c>
       <c r="B30" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130020595</v>
+        <v>130020603</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,30 +4048,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4079,10 +4075,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452980</v>
+        <v>452890</v>
       </c>
       <c r="R31" t="n">
-        <v>7044123</v>
+        <v>7044184</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4119,7 +4115,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Växer på en gammal grov sälg.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4139,22 +4135,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4172,10 +4168,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130020603</v>
+        <v>130020595</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4183,26 +4179,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452890</v>
+        <v>452980</v>
       </c>
       <c r="R32" t="n">
-        <v>7044184</v>
+        <v>7044123</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Växer på en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
         <v>130021380</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>130020596</v>
       </c>
       <c r="B34" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130020602</v>
+        <v>130021386</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>89005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,37 +978,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452837</v>
+        <v>452983</v>
       </c>
       <c r="R5" t="n">
-        <v>7044165</v>
+        <v>7044206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,51 +1046,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130020606</v>
+        <v>130020602</v>
       </c>
       <c r="B6" t="n">
         <v>79088</v>
@@ -1131,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452902</v>
+        <v>452837</v>
       </c>
       <c r="R6" t="n">
-        <v>7044130</v>
+        <v>7044165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,11 +1138,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riktigt på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021386</v>
+        <v>130020606</v>
       </c>
       <c r="B7" t="n">
-        <v>89005</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,34 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452983</v>
+        <v>452902</v>
       </c>
       <c r="R7" t="n">
-        <v>7044206</v>
+        <v>7044130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,24 +1266,55 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riktigt på gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2318,52 +2318,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130020592</v>
+        <v>130021384</v>
       </c>
       <c r="B16" t="n">
-        <v>92059</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452937</v>
+        <v>452906</v>
       </c>
       <c r="R16" t="n">
-        <v>7044107</v>
+        <v>7044060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,7 +2393,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer i en grov granlåga.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,51 +2402,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130021384</v>
+        <v>130020605</v>
       </c>
       <c r="B17" t="n">
         <v>79088</v>
@@ -2482,16 +2449,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452906</v>
+        <v>452930</v>
       </c>
       <c r="R17" t="n">
-        <v>7044060</v>
+        <v>7044128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,7 +2498,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt och med långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,28 +2507,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130020605</v>
+        <v>130021369</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2566,37 +2562,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452930</v>
+        <v>452811</v>
       </c>
       <c r="R18" t="n">
-        <v>7044128</v>
+        <v>7044305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,93 +2620,65 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130020594</v>
+        <v>130020592</v>
       </c>
       <c r="B19" t="n">
-        <v>97669</v>
+        <v>92059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2725,10 +2686,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452919</v>
+        <v>452937</v>
       </c>
       <c r="R19" t="n">
-        <v>7044111</v>
+        <v>7044107</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2763,6 +2724,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer i en grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2776,6 +2742,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2928,41 +2914,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021369</v>
+        <v>130020594</v>
       </c>
       <c r="B21" t="n">
-        <v>91626</v>
+        <v>97669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452811</v>
+        <v>452919</v>
       </c>
       <c r="R21" t="n">
-        <v>7044305</v>
+        <v>7044111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,18 +2997,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021379</v>
+        <v>130021370</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3741,23 +3741,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3765,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452770</v>
+        <v>452883</v>
       </c>
       <c r="R28" t="n">
-        <v>7044215</v>
+        <v>7044262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3801,11 +3797,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021370</v>
+        <v>130021379</v>
       </c>
       <c r="B29" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3843,19 +3834,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452883</v>
+        <v>452770</v>
       </c>
       <c r="R29" t="n">
-        <v>7044262</v>
+        <v>7044215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3899,6 +3894,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021371</v>
+        <v>130021368</v>
       </c>
       <c r="B2" t="n">
-        <v>91626</v>
+        <v>91620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453025</v>
+        <v>452923</v>
       </c>
       <c r="R2" t="n">
-        <v>7044138</v>
+        <v>7044088</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021368</v>
+        <v>130021371</v>
       </c>
       <c r="B3" t="n">
-        <v>91620</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +783,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452923</v>
+        <v>453025</v>
       </c>
       <c r="R3" t="n">
-        <v>7044088</v>
+        <v>7044138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2057,37 +2057,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130020601</v>
+        <v>130020597</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2095,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452820</v>
+        <v>452980</v>
       </c>
       <c r="R14" t="n">
-        <v>7044247</v>
+        <v>7044127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,6 +2137,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2150,22 +2159,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2183,41 +2192,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130020597</v>
+        <v>130020601</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452980</v>
+        <v>452820</v>
       </c>
       <c r="R15" t="n">
-        <v>7044127</v>
+        <v>7044247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,11 +2268,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2285,22 +2285,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,45 +2318,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021384</v>
+        <v>130020592</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>92059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452906</v>
+        <v>452937</v>
       </c>
       <c r="R16" t="n">
-        <v>7044060</v>
+        <v>7044107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,7 +2400,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,25 +2409,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130020605</v>
+        <v>130021384</v>
       </c>
       <c r="B17" t="n">
         <v>79088</v>
@@ -2449,19 +2482,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452930</v>
+        <v>452906</v>
       </c>
       <c r="R17" t="n">
-        <v>7044128</v>
+        <v>7044060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,7 +2528,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,54 +2537,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130021369</v>
+        <v>130020605</v>
       </c>
       <c r="B18" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,30 +2566,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452811</v>
+        <v>452930</v>
       </c>
       <c r="R18" t="n">
-        <v>7044305</v>
+        <v>7044128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,65 +2631,93 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt och med långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130020592</v>
+        <v>130020594</v>
       </c>
       <c r="B19" t="n">
-        <v>92059</v>
+        <v>97669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2686,10 +2725,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452937</v>
+        <v>452919</v>
       </c>
       <c r="R19" t="n">
-        <v>7044107</v>
+        <v>7044111</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,11 +2763,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växer i en grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2742,26 +2776,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2914,49 +2928,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130020594</v>
+        <v>130021369</v>
       </c>
       <c r="B21" t="n">
-        <v>97669</v>
+        <v>91626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452919</v>
+        <v>452811</v>
       </c>
       <c r="R21" t="n">
-        <v>7044111</v>
+        <v>7044305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,24 +3003,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130020595</v>
+        <v>130021380</v>
       </c>
       <c r="B32" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4179,41 +4179,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452980</v>
+        <v>452797</v>
       </c>
       <c r="R32" t="n">
-        <v>7044123</v>
+        <v>7044290</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4250,7 +4243,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer på en gammal grov sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,54 +4252,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130021380</v>
+        <v>130020595</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4314,34 +4281,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452797</v>
+        <v>452980</v>
       </c>
       <c r="R33" t="n">
-        <v>7044290</v>
+        <v>7044123</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4378,7 +4352,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer på en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,18 +4361,44 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130021368</v>
       </c>
       <c r="B2" t="n">
-        <v>91620</v>
+        <v>91637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130021371</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>130021381</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021386</v>
+        <v>130020606</v>
       </c>
       <c r="B5" t="n">
-        <v>89005</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,34 +978,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452983</v>
+        <v>452902</v>
       </c>
       <c r="R5" t="n">
-        <v>7044206</v>
+        <v>7044130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1040,34 +1043,65 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riktigt på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130020602</v>
+        <v>130021386</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>89022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,37 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452837</v>
+        <v>452983</v>
       </c>
       <c r="R6" t="n">
-        <v>7044165</v>
+        <v>7044206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,54 +1177,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130020606</v>
+        <v>130020602</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452902</v>
+        <v>452837</v>
       </c>
       <c r="R7" t="n">
-        <v>7044130</v>
+        <v>7044165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,11 +1269,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riktigt på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130020604</v>
+        <v>130021364</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,37 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452984</v>
+        <v>452814</v>
       </c>
       <c r="R8" t="n">
-        <v>7044154</v>
+        <v>7044305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1396,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,54 +1405,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130020599</v>
+        <v>130021365</v>
       </c>
       <c r="B9" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,37 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452976</v>
+        <v>452913</v>
       </c>
       <c r="R9" t="n">
-        <v>7044174</v>
+        <v>7044076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,54 +1507,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130021364</v>
+        <v>130020599</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>91643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,34 +1536,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452814</v>
+        <v>452976</v>
       </c>
       <c r="R10" t="n">
-        <v>7044305</v>
+        <v>7044174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1603,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,28 +1612,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021365</v>
+        <v>130020604</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,34 +1667,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452913</v>
+        <v>452984</v>
       </c>
       <c r="R11" t="n">
-        <v>7044076</v>
+        <v>7044154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1734,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,18 +1743,44 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
         <v>130020598</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>130020588</v>
       </c>
       <c r="B13" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>130020597</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>130020601</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>130020592</v>
       </c>
       <c r="B16" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130021384</v>
+        <v>130020591</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>80195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,34 +2464,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452906</v>
+        <v>452849</v>
       </c>
       <c r="R17" t="n">
-        <v>7044060</v>
+        <v>7044229</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,7 +2535,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,55 +2544,82 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130020605</v>
+        <v>130020594</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>97686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2593,10 +2627,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452930</v>
+        <v>452919</v>
       </c>
       <c r="R18" t="n">
-        <v>7044128</v>
+        <v>7044111</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,11 +2665,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2649,26 +2678,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2686,49 +2695,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130020594</v>
+        <v>130021369</v>
       </c>
       <c r="B19" t="n">
-        <v>97669</v>
+        <v>91643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452919</v>
+        <v>452811</v>
       </c>
       <c r="R19" t="n">
-        <v>7044111</v>
+        <v>7044305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2769,34 +2770,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130020591</v>
+        <v>130021384</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,41 +2799,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452849</v>
+        <v>452906</v>
       </c>
       <c r="R20" t="n">
-        <v>7044229</v>
+        <v>7044060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2875,7 +2863,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,54 +2872,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021369</v>
+        <v>130020605</v>
       </c>
       <c r="B21" t="n">
-        <v>91626</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2939,30 +2901,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452811</v>
+        <v>452930</v>
       </c>
       <c r="R21" t="n">
-        <v>7044305</v>
+        <v>7044128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,34 +2966,65 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt och med långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130020600</v>
+        <v>130021383</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,19 +3050,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452761</v>
+        <v>453051</v>
       </c>
       <c r="R22" t="n">
-        <v>7044258</v>
+        <v>7044264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,95 +3094,81 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021383</v>
+        <v>130020589</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>80223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453051</v>
+        <v>452853</v>
       </c>
       <c r="R23" t="n">
-        <v>7044264</v>
+        <v>7044232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3205,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,59 +3214,81 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130020589</v>
+        <v>130020600</v>
       </c>
       <c r="B24" t="n">
-        <v>80222</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3291,10 +3296,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452853</v>
+        <v>452761</v>
       </c>
       <c r="R24" t="n">
-        <v>7044232</v>
+        <v>7044258</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3329,11 +3334,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3500,7 +3500,7 @@
         <v>130020607</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>130021382</v>
       </c>
       <c r="B27" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>130021370</v>
       </c>
       <c r="B28" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>130021379</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>130020593</v>
       </c>
       <c r="B30" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130020603</v>
+        <v>130021380</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,19 +4066,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452890</v>
+        <v>452797</v>
       </c>
       <c r="R31" t="n">
-        <v>7044184</v>
+        <v>7044290</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4115,7 +4112,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4124,54 +4121,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021380</v>
+        <v>130020595</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>80194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4179,34 +4150,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452797</v>
+        <v>452980</v>
       </c>
       <c r="R32" t="n">
-        <v>7044290</v>
+        <v>7044123</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4243,7 +4221,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer på en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4252,28 +4230,54 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130020595</v>
+        <v>130020603</v>
       </c>
       <c r="B33" t="n">
-        <v>80193</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4281,30 +4285,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452980</v>
+        <v>452890</v>
       </c>
       <c r="R33" t="n">
-        <v>7044123</v>
+        <v>7044184</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer på en gammal grov sälg.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
         <v>130020596</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021368</v>
+        <v>130021371</v>
       </c>
       <c r="B2" t="n">
-        <v>91653</v>
+        <v>91659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452923</v>
+        <v>453025</v>
       </c>
       <c r="R2" t="n">
-        <v>7044088</v>
+        <v>7044138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021371</v>
+        <v>130021368</v>
       </c>
       <c r="B3" t="n">
-        <v>91659</v>
+        <v>91653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453025</v>
+        <v>452923</v>
       </c>
       <c r="R3" t="n">
-        <v>7044138</v>
+        <v>7044088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021364</v>
+        <v>130020599</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,34 +1332,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452814</v>
+        <v>452976</v>
       </c>
       <c r="R8" t="n">
-        <v>7044305</v>
+        <v>7044174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1399,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,25 +1408,51 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021365</v>
+        <v>130021364</v>
       </c>
       <c r="B9" t="n">
         <v>57741</v>
@@ -1458,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452913</v>
+        <v>452814</v>
       </c>
       <c r="R9" t="n">
-        <v>7044076</v>
+        <v>7044305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1527,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130020604</v>
+        <v>130021365</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,37 +1565,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452984</v>
+        <v>452913</v>
       </c>
       <c r="R10" t="n">
-        <v>7044154</v>
+        <v>7044076</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,54 +1638,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130020599</v>
+        <v>130020604</v>
       </c>
       <c r="B11" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,26 +1667,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452976</v>
+        <v>452984</v>
       </c>
       <c r="R11" t="n">
-        <v>7044174</v>
+        <v>7044154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -3730,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021379</v>
+        <v>130021370</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>91659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3741,23 +3741,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3765,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452770</v>
+        <v>452883</v>
       </c>
       <c r="R28" t="n">
-        <v>7044215</v>
+        <v>7044262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3801,11 +3797,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021370</v>
+        <v>130021379</v>
       </c>
       <c r="B29" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3843,19 +3834,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452883</v>
+        <v>452770</v>
       </c>
       <c r="R29" t="n">
-        <v>7044262</v>
+        <v>7044215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3899,6 +3894,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130021371</v>
       </c>
       <c r="B2" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>130021368</v>
       </c>
       <c r="B3" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130020602</v>
+        <v>130021386</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>89038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,37 +978,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452837</v>
+        <v>452983</v>
       </c>
       <c r="R5" t="n">
-        <v>7044165</v>
+        <v>7044206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,51 +1046,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130020606</v>
+        <v>130020602</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1131,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452902</v>
+        <v>452837</v>
       </c>
       <c r="R6" t="n">
-        <v>7044130</v>
+        <v>7044165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,11 +1138,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riktigt på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021386</v>
+        <v>130020606</v>
       </c>
       <c r="B7" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,34 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452983</v>
+        <v>452902</v>
       </c>
       <c r="R7" t="n">
-        <v>7044206</v>
+        <v>7044130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,24 +1266,55 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riktigt på gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
         <v>130020599</v>
       </c>
       <c r="B8" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>130020598</v>
       </c>
       <c r="B12" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>130020588</v>
       </c>
       <c r="B13" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,37 +2057,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130020601</v>
+        <v>130020597</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>80236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2095,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452820</v>
+        <v>452980</v>
       </c>
       <c r="R14" t="n">
-        <v>7044247</v>
+        <v>7044127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,6 +2137,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2150,22 +2159,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2183,41 +2192,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130020597</v>
+        <v>130020601</v>
       </c>
       <c r="B15" t="n">
-        <v>80236</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452980</v>
+        <v>452820</v>
       </c>
       <c r="R15" t="n">
-        <v>7044127</v>
+        <v>7044247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,11 +2268,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2285,22 +2285,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021369</v>
+        <v>130020591</v>
       </c>
       <c r="B16" t="n">
-        <v>91659</v>
+        <v>80201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,30 +2329,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452811</v>
+        <v>452849</v>
       </c>
       <c r="R16" t="n">
-        <v>7044305</v>
+        <v>7044229</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,73 +2398,96 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130020594</v>
+        <v>130021369</v>
       </c>
       <c r="B17" t="n">
-        <v>97702</v>
+        <v>91661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452919</v>
+        <v>452811</v>
       </c>
       <c r="R17" t="n">
-        <v>7044111</v>
+        <v>7044305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,69 +2528,70 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130021384</v>
+        <v>130020592</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>92094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452906</v>
+        <v>452937</v>
       </c>
       <c r="R18" t="n">
-        <v>7044060</v>
+        <v>7044107</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2628,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,25 +2637,51 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130020605</v>
+        <v>130021384</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2649,19 +2710,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452930</v>
+        <v>452906</v>
       </c>
       <c r="R19" t="n">
-        <v>7044128</v>
+        <v>7044060</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,7 +2756,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,85 +2765,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130020592</v>
+        <v>130020605</v>
       </c>
       <c r="B20" t="n">
-        <v>92092</v>
+        <v>79095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2793,10 +2821,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452937</v>
+        <v>452930</v>
       </c>
       <c r="R20" t="n">
-        <v>7044107</v>
+        <v>7044128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,7 +2861,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växer i en grov granlåga.</t>
+          <t>Rikligt och med långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,12 +2891,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2886,41 +2914,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130020591</v>
+        <v>130020594</v>
       </c>
       <c r="B21" t="n">
-        <v>80201</v>
+        <v>97704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2928,10 +2953,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452849</v>
+        <v>452919</v>
       </c>
       <c r="R21" t="n">
-        <v>7044229</v>
+        <v>7044111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,11 +2991,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2984,26 +3004,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3021,37 +3021,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130020600</v>
+        <v>130020589</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452761</v>
+        <v>452853</v>
       </c>
       <c r="R22" t="n">
-        <v>7044258</v>
+        <v>7044232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,6 +3101,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3114,22 +3123,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3147,7 +3156,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021383</v>
+        <v>130020600</v>
       </c>
       <c r="B23" t="n">
         <v>79095</v>
@@ -3176,16 +3185,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453051</v>
+        <v>452761</v>
       </c>
       <c r="R23" t="n">
-        <v>7044264</v>
+        <v>7044258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3220,81 +3232,95 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130020589</v>
+        <v>130021383</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452853</v>
+        <v>453051</v>
       </c>
       <c r="R24" t="n">
-        <v>7044232</v>
+        <v>7044264</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3331,7 +3357,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,44 +3366,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
         <v>130021370</v>
       </c>
       <c r="B28" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>130020593</v>
       </c>
       <c r="B30" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130021380</v>
+        <v>130020595</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,34 +4048,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452797</v>
+        <v>452980</v>
       </c>
       <c r="R31" t="n">
-        <v>7044290</v>
+        <v>7044123</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4112,7 +4119,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer på en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4121,25 +4128,51 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130020603</v>
+        <v>130021380</v>
       </c>
       <c r="B32" t="n">
         <v>79095</v>
@@ -4168,19 +4201,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452890</v>
+        <v>452797</v>
       </c>
       <c r="R32" t="n">
-        <v>7044184</v>
+        <v>7044290</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4217,7 +4247,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,54 +4256,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130020595</v>
+        <v>130020603</v>
       </c>
       <c r="B33" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4281,30 +4285,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452980</v>
+        <v>452890</v>
       </c>
       <c r="R33" t="n">
-        <v>7044123</v>
+        <v>7044184</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer på en gammal grov sälg.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021371</v>
+        <v>130021368</v>
       </c>
       <c r="B2" t="n">
-        <v>91661</v>
+        <v>91742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453025</v>
+        <v>452923</v>
       </c>
       <c r="R2" t="n">
-        <v>7044138</v>
+        <v>7044088</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021368</v>
+        <v>130021371</v>
       </c>
       <c r="B3" t="n">
-        <v>91655</v>
+        <v>91748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +783,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452923</v>
+        <v>453025</v>
       </c>
       <c r="R3" t="n">
-        <v>7044088</v>
+        <v>7044138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
         <v>130021381</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>130021386</v>
       </c>
       <c r="B5" t="n">
-        <v>89038</v>
+        <v>89125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>130020602</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130020606</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130020599</v>
+        <v>130020604</v>
       </c>
       <c r="B8" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,26 +1332,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452976</v>
+        <v>452984</v>
       </c>
       <c r="R8" t="n">
-        <v>7044174</v>
+        <v>7044154</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021364</v>
+        <v>130020599</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452814</v>
+        <v>452976</v>
       </c>
       <c r="R9" t="n">
-        <v>7044305</v>
+        <v>7044174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1530,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,28 +1539,54 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130021365</v>
+        <v>130021364</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452913</v>
+        <v>452814</v>
       </c>
       <c r="R10" t="n">
-        <v>7044076</v>
+        <v>7044305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1658,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130020604</v>
+        <v>130021365</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,37 +1696,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452984</v>
+        <v>452913</v>
       </c>
       <c r="R11" t="n">
-        <v>7044154</v>
+        <v>7044076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1760,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,44 +1769,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
         <v>130020598</v>
       </c>
       <c r="B12" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>130020588</v>
       </c>
       <c r="B13" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>130020597</v>
       </c>
       <c r="B14" t="n">
-        <v>80236</v>
+        <v>80321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>130020601</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130020591</v>
+        <v>130021384</v>
       </c>
       <c r="B16" t="n">
-        <v>80201</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,41 +2329,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452849</v>
+        <v>452906</v>
       </c>
       <c r="R16" t="n">
-        <v>7044229</v>
+        <v>7044060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,7 +2393,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,44 +2402,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2456,7 +2423,7 @@
         <v>130021369</v>
       </c>
       <c r="B17" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,39 +2513,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130020592</v>
+        <v>130020591</v>
       </c>
       <c r="B18" t="n">
-        <v>92094</v>
+        <v>80286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2588,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452937</v>
+        <v>452849</v>
       </c>
       <c r="R18" t="n">
-        <v>7044107</v>
+        <v>7044229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2628,7 +2595,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Växer i en grov granlåga.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,22 +2615,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2681,45 +2648,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021384</v>
+        <v>130020592</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452906</v>
+        <v>452937</v>
       </c>
       <c r="R19" t="n">
-        <v>7044060</v>
+        <v>7044107</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2730,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,55 +2739,82 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130020605</v>
+        <v>130020594</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2821,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452930</v>
+        <v>452919</v>
       </c>
       <c r="R20" t="n">
-        <v>7044128</v>
+        <v>7044111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,11 +2860,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2877,26 +2873,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2914,38 +2890,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130020594</v>
+        <v>130020605</v>
       </c>
       <c r="B21" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2953,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452919</v>
+        <v>452930</v>
       </c>
       <c r="R21" t="n">
-        <v>7044111</v>
+        <v>7044128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,6 +2966,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt och med långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3004,6 +2984,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3021,52 +3021,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130020589</v>
+        <v>130021383</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452853</v>
+        <v>453051</v>
       </c>
       <c r="R22" t="n">
-        <v>7044232</v>
+        <v>7044264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3103,7 +3096,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3112,44 +3105,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3159,7 +3126,7 @@
         <v>130020600</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3282,45 +3249,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021383</v>
+        <v>130020589</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>80314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453051</v>
+        <v>452853</v>
       </c>
       <c r="R24" t="n">
-        <v>7044264</v>
+        <v>7044232</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3357,7 +3331,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,18 +3340,44 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
         <v>130021367</v>
       </c>
       <c r="B25" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>130020607</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>130021382</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>130021370</v>
       </c>
       <c r="B28" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>130021379</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>130020593</v>
       </c>
       <c r="B30" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>130020595</v>
       </c>
       <c r="B31" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021380</v>
+        <v>130020603</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4201,16 +4201,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452797</v>
+        <v>452890</v>
       </c>
       <c r="R32" t="n">
-        <v>7044290</v>
+        <v>7044184</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4247,7 +4250,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4256,28 +4259,54 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130020603</v>
+        <v>130021380</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,19 +4332,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452890</v>
+        <v>452797</v>
       </c>
       <c r="R33" t="n">
-        <v>7044184</v>
+        <v>7044290</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4352,7 +4378,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4361,44 +4387,18 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
         <v>130020596</v>
       </c>
       <c r="B34" t="n">
-        <v>80236</v>
+        <v>80321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021371</v>
+        <v>130021386</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453025</v>
+        <v>452983</v>
       </c>
       <c r="R2" t="n">
-        <v>7044138</v>
+        <v>7044206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021368</v>
+        <v>130020598</v>
       </c>
       <c r="B3" t="n">
-        <v>91742</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,34 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452923</v>
+        <v>452953</v>
       </c>
       <c r="R3" t="n">
-        <v>7044088</v>
+        <v>7044143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,34 +852,65 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021381</v>
+        <v>130020588</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,34 +918,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452915</v>
+        <v>452939</v>
       </c>
       <c r="R4" t="n">
-        <v>7044244</v>
+        <v>7044096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -949,50 +998,76 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021386</v>
+        <v>130021368</v>
       </c>
       <c r="B5" t="n">
-        <v>89124</v>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452983</v>
+        <v>452923</v>
       </c>
       <c r="R5" t="n">
-        <v>7044206</v>
+        <v>7044088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130020606</v>
+        <v>130020592</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,26 +1150,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1102,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452902</v>
+        <v>452937</v>
       </c>
       <c r="R6" t="n">
-        <v>7044130</v>
+        <v>7044107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Riktigt på gran.</t>
+          <t>Växer i en grov granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,12 +1251,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1195,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130020602</v>
+        <v>130020591</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,26 +1285,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1233,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452837</v>
+        <v>452849</v>
       </c>
       <c r="R7" t="n">
-        <v>7044165</v>
+        <v>7044229</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1354,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1288,22 +1376,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1321,37 +1409,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130020599</v>
+        <v>130020600</v>
       </c>
       <c r="B8" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452976</v>
+        <v>452761</v>
       </c>
       <c r="R8" t="n">
-        <v>7044174</v>
+        <v>7044258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,11 +1485,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående gran med 69 cm i brösthöjdsdiameter. Granen indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1429,12 +1512,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,14 +1535,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130020604</v>
+        <v>130020601</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1490,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452984</v>
+        <v>452820</v>
       </c>
       <c r="R9" t="n">
-        <v>7044154</v>
+        <v>7044247</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,11 +1611,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1560,12 +1638,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1583,45 +1661,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130021364</v>
+        <v>130020602</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452814</v>
+        <v>452837</v>
       </c>
       <c r="R10" t="n">
-        <v>7044305</v>
+        <v>7044165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,74 +1737,98 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021365</v>
+        <v>130020603</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452913</v>
+        <v>452890</v>
       </c>
       <c r="R11" t="n">
-        <v>7044076</v>
+        <v>7044184</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1865,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,59 +1874,81 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130020598</v>
+        <v>130020604</v>
       </c>
       <c r="B12" t="n">
-        <v>91724</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1829,10 +1956,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452953</v>
+        <v>452984</v>
       </c>
       <c r="R12" t="n">
-        <v>7044143</v>
+        <v>7044154</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1996,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran med full längd.</t>
+          <t>Här växer garnlav på en stående död gran med full längd och 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,41 +2049,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130020588</v>
+        <v>130020605</v>
       </c>
       <c r="B13" t="n">
-        <v>91728</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1964,10 +2087,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452939</v>
+        <v>452930</v>
       </c>
       <c r="R13" t="n">
-        <v>7044096</v>
+        <v>7044128</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2127,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer i en grov granlåga.</t>
+          <t>Rikligt och med långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,12 +2157,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2057,14 +2180,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130020601</v>
+        <v>130020606</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2095,10 +2218,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452820</v>
+        <v>452902</v>
       </c>
       <c r="R14" t="n">
-        <v>7044247</v>
+        <v>7044130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,6 +2254,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riktigt på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,41 +2311,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130020597</v>
+        <v>130020607</v>
       </c>
       <c r="B15" t="n">
-        <v>80321</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2225,10 +2349,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452980</v>
+        <v>452888</v>
       </c>
       <c r="R15" t="n">
-        <v>7044127</v>
+        <v>7044076</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,7 +2389,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,22 +2409,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2318,30 +2442,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021369</v>
+        <v>130021379</v>
       </c>
       <c r="B16" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2349,10 +2477,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452811</v>
+        <v>452770</v>
       </c>
       <c r="R16" t="n">
-        <v>7044305</v>
+        <v>7044215</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2385,6 +2513,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,14 +2544,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130021384</v>
+        <v>130021380</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2446,10 +2579,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452906</v>
+        <v>452797</v>
       </c>
       <c r="R17" t="n">
-        <v>7044060</v>
+        <v>7044290</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,14 +2646,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130020605</v>
+        <v>130021381</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2542,19 +2675,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452930</v>
+        <v>452915</v>
       </c>
       <c r="R18" t="n">
-        <v>7044128</v>
+        <v>7044244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2721,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,54 +2730,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130020592</v>
+        <v>130021382</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,41 +2759,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452937</v>
+        <v>452972</v>
       </c>
       <c r="R19" t="n">
-        <v>7044107</v>
+        <v>7044214</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,7 +2823,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Växer i en grov granlåga.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,96 +2832,63 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130020591</v>
+        <v>130021383</v>
       </c>
       <c r="B20" t="n">
-        <v>80286</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452849</v>
+        <v>453051</v>
       </c>
       <c r="R20" t="n">
-        <v>7044229</v>
+        <v>7044264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,7 +2925,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,93 +2934,63 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130020594</v>
+        <v>130021384</v>
       </c>
       <c r="B21" t="n">
-        <v>97791</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452919</v>
+        <v>452906</v>
       </c>
       <c r="R21" t="n">
-        <v>7044111</v>
+        <v>7044060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,40 +3025,39 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130020600</v>
+        <v>130020595</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3032,26 +3065,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3059,10 +3096,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452761</v>
+        <v>452980</v>
       </c>
       <c r="R22" t="n">
-        <v>7044258</v>
+        <v>7044123</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,6 +3134,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer på en gammal grov sälg.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3114,22 +3156,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3147,45 +3189,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021383</v>
+        <v>130020589</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453051</v>
+        <v>452853</v>
       </c>
       <c r="R23" t="n">
-        <v>7044264</v>
+        <v>7044232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3271,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,28 +3280,54 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130020589</v>
+        <v>130020596</v>
       </c>
       <c r="B24" t="n">
-        <v>80314</v>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,21 +3335,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3291,10 +3366,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452853</v>
+        <v>452855</v>
       </c>
       <c r="R24" t="n">
-        <v>7044232</v>
+        <v>7044233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,10 +3459,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130021367</v>
+        <v>130020597</v>
       </c>
       <c r="B25" t="n">
-        <v>57930</v>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,40 +3470,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
@@ -3438,7 +3504,7 @@
         <v>452980</v>
       </c>
       <c r="R25" t="n">
-        <v>7044207</v>
+        <v>7044127</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3473,34 +3539,65 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130020607</v>
+        <v>130021364</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,37 +3605,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452888</v>
+        <v>452814</v>
       </c>
       <c r="R26" t="n">
-        <v>7044076</v>
+        <v>7044305</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3575,7 +3669,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,54 +3678,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130021382</v>
+        <v>130021365</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,21 +3707,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3663,10 +3731,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452972</v>
+        <v>452913</v>
       </c>
       <c r="R27" t="n">
-        <v>7044214</v>
+        <v>7044076</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3703,7 +3771,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,10 +3798,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021370</v>
+        <v>130021367</v>
       </c>
       <c r="B28" t="n">
-        <v>91748</v>
+        <v>58057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3741,30 +3809,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452883</v>
+        <v>452980</v>
       </c>
       <c r="R28" t="n">
-        <v>7044262</v>
+        <v>7044207</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,45 +3911,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021379</v>
+        <v>130020593</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>97983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452770</v>
+        <v>452847</v>
       </c>
       <c r="R29" t="n">
-        <v>7044215</v>
+        <v>7044242</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3898,7 +3990,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>I gammal granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,28 +3999,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130020593</v>
+        <v>130020594</v>
       </c>
       <c r="B30" t="n">
-        <v>97791</v>
+        <v>97983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,10 +4062,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452847</v>
+        <v>452919</v>
       </c>
       <c r="R30" t="n">
-        <v>7044242</v>
+        <v>7044111</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4002,11 +4100,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>I gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4034,509 +4127,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>130021380</v>
-      </c>
-      <c r="B31" t="n">
-        <v>79180</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Almåsaberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>452797</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7044290</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>130020603</v>
-      </c>
-      <c r="B32" t="n">
-        <v>79180</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Almåsaberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>452890</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7044184</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>130020595</v>
-      </c>
-      <c r="B33" t="n">
-        <v>80285</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Almåsaberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>452980</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7044123</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grov sälg.</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>130020596</v>
-      </c>
-      <c r="B34" t="n">
-        <v>80321</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Almåsaberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>452855</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7044233</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54353-2025 artfynd.xlsx
+++ b/artfynd/A 54353-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021386</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020588</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021368</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020592</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1406,6 +1436,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020591</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1532,6 +1567,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020600</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1658,6 +1698,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020601</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1784,6 +1829,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020602</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1915,6 +1965,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020603</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2046,6 +2101,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020604</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2177,6 +2237,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020605</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2308,6 +2373,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020606</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2439,6 +2509,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020607</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2541,6 +2616,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021379</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2643,6 +2723,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021380</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2745,6 +2830,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021381</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2847,6 +2937,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021382</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2949,6 +3044,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021383</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3051,6 +3151,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021384</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3186,6 +3291,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020595</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3321,6 +3431,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020589</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3456,6 +3571,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020596</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3591,6 +3711,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020597</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3693,6 +3818,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021364</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3795,6 +3925,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021365</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3908,6 +4043,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021367</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4020,6 +4160,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020593</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4127,8 +4272,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>